--- a/data/Recruitment_Service_Quality_Evaluation.xlsx
+++ b/data/Recruitment_Service_Quality_Evaluation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CC39222-A6C5-4ED7-8C3E-39599BD7E489}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF727B4-C4DD-4FDC-AE1B-A77E53863797}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
   <si>
     <t>Id</t>
   </si>
@@ -177,13 +177,69 @@
   </si>
   <si>
     <t xml:space="preserve">อาจจะต้องเตรียมรถส่งพนักงานไปขึ้นรถโดยสารหน้านิคมอุตสาหกรรม สำหรับน้องๆที่มาสัมภาษณ์ที่ไม่มีรถส่วนตัว หรือคนมารอรับ </t>
+  </si>
+  <si>
+    <t>sirinun.y@kubota.com</t>
+  </si>
+  <si>
+    <t>Sirinun Yantarakoses</t>
+  </si>
+  <si>
+    <t>Service Business Intelligence</t>
+  </si>
+  <si>
+    <t>สรรหาผู้สมัครได้มีคุณภาพ และมีปริมาณมากเพียงพอให้คัดเลือก</t>
+  </si>
+  <si>
+    <t>การสรรหาภายใน อยากให้กำหนดเวลาและเวลาเริ่มงานได้ชัดเจนเหมือนสรรหาภายนอกค่ะ บางทีเคสต้องรอพนักงานมาเติมเต็มจากต้นสังกัดทำให้ระยะเวลายืดออกไปค่ะ</t>
+  </si>
+  <si>
+    <t>piyapong.t@kubota.com</t>
+  </si>
+  <si>
+    <t>Piyapong Tungsakulwijarn</t>
+  </si>
+  <si>
+    <t>Service Business Intelligence Executive</t>
+  </si>
+  <si>
+    <t>มีการติดตามและอัพเดทอย่างใกล้ชิด</t>
+  </si>
+  <si>
+    <t>Software Developer</t>
+  </si>
+  <si>
+    <t>กระบวนการสรรหาเร็วขึ้น</t>
+  </si>
+  <si>
+    <t>แจ้งสถานะอย่างสม่ำเสมอ</t>
+  </si>
+  <si>
+    <t>nisaras.y@kubota.com</t>
+  </si>
+  <si>
+    <t>Nisaras Yimlamay</t>
+  </si>
+  <si>
+    <t>Risk Management Officer</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>การรับฟังความต้องการลูกค้าและจัดการได้ตามความต้องการ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ้าพนักงานที่ลาออกไปแล้ว ควรกำหนด KPI ตั้งแต่พนักงานลากจนถึงเสนอขอนุมัติจาก President ด้วย 
+ไม่ใช่วัดระยะเวลาเฉพาะหลังจากที่ President อนุมัติ 
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -232,6 +288,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -303,8 +362,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L8" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L12" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L12" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="11">
       <extLst>
@@ -394,7 +453,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zp3wzWXIQk-QHTLT2NP2D5hypM5lSwJOkKByoup55W5URTUySUVQWU5HTVpRQ01aNEZJVkpOQ040WS4u" isFormConnected="1" maxResponseId="7" latestEventMarker="5">
+      <xlmsforms:msForm id="zp3wzWXIQk-QHTLT2NP2D5hypM5lSwJOkKByoup55W5URTUySUVQWU5HTVpRQ01aNEZJVkpOQ040WS4u" isFormConnected="1" maxResponseId="11" latestEventMarker="9">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -710,16 +769,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.9"/>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="10" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="100.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="180.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.75" style="1"/>
+    <col min="11" max="11" width="100.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="180.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -757,7 +816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -795,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -833,7 +892,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -871,7 +930,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -909,8 +968,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2">
@@ -947,8 +1006,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="6">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2">
@@ -985,8 +1044,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="6">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2">
@@ -1021,6 +1080,158 @@
       </c>
       <c r="L8" s="4" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46213.5304861111</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46213.546539351897</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46216.473217592596</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46216.473749999997</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46218.822881944398</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46218.824826388904</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46225.9445949074</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46225.946111111101</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data/Recruitment_Service_Quality_Evaluation.xlsx
+++ b/data/Recruitment_Service_Quality_Evaluation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF727B4-C4DD-4FDC-AE1B-A77E53863797}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28C1EFEE-42A4-4CF0-8248-2C076126FDD9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="73">
   <si>
     <t>Id</t>
   </si>
@@ -233,6 +233,30 @@
     <t xml:space="preserve">ถ้าพนักงานที่ลาออกไปแล้ว ควรกำหนด KPI ตั้งแต่พนักงานลากจนถึงเสนอขอนุมัติจาก President ด้วย 
 ไม่ใช่วัดระยะเวลาเฉพาะหลังจากที่ President อนุมัติ 
 </t>
+  </si>
+  <si>
+    <t>naratip.p@kubota.com</t>
+  </si>
+  <si>
+    <t>Naratip Panichpongpan</t>
+  </si>
+  <si>
+    <t>Parts Localization &amp; Strategic</t>
+  </si>
+  <si>
+    <t>รวดเร็ว</t>
+  </si>
+  <si>
+    <t>ยังไม่มี</t>
+  </si>
+  <si>
+    <t>วางแผนอะไหล่</t>
+  </si>
+  <si>
+    <t>คัดเลือกคนมาเข้าสัมภาษณ์มีคุณภาพดีมาก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">น่าจะมีเงินช่วยเหลือค่าเดินทางให้กับน้องที่มาสัมภาษณ์ เพราะบริษัทเราอยู่ไกลและเดินทางมาลำบากถ้าไม่มีรถส่วนตัวมาเอง </t>
   </si>
 </sst>
 </file>
@@ -285,11 +309,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -362,8 +386,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L12" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L12" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L14" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L14" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="11">
       <extLst>
@@ -453,7 +477,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zp3wzWXIQk-QHTLT2NP2D5hypM5lSwJOkKByoup55W5URTUySUVQWU5HTVpRQ01aNEZJVkpOQ040WS4u" isFormConnected="1" maxResponseId="11" latestEventMarker="9">
+      <xlmsforms:msForm id="zp3wzWXIQk-QHTLT2NP2D5hypM5lSwJOkKByoup55W5URTUySUVQWU5HTVpRQ01aNEZJVkpOQ040WS4u" isFormConnected="1" maxResponseId="13" latestEventMarker="11">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -769,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="10" width="20" style="1" bestFit="1" customWidth="1"/>
@@ -1083,7 +1107,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2">
@@ -1121,7 +1145,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2">
@@ -1159,7 +1183,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2">
@@ -1197,7 +1221,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2">
@@ -1230,8 +1254,84 @@
       <c r="K12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="6" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46251.371979166703</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46251.3733333333</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46251.4061574074</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46251.409861111097</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/data/Recruitment_Service_Quality_Evaluation.xlsx
+++ b/data/Recruitment_Service_Quality_Evaluation.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kubotagroup-my.sharepoint.com/personal/lapat_j_kubota_com/Documents/Documents/Recruitment Tools/Dashboard Data Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28C1EFEE-42A4-4CF0-8248-2C076126FDD9}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96B4DF22-44EA-4328-AC9C-13F6A78B8555}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Satisfaction Scores Rate" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="81">
   <si>
     <t>Id</t>
   </si>
@@ -68,9 +69,6 @@
     <t>ด้านการบริการ (โดย 1 หมายถึงไม่เห็นด้วย และ 4 เห็นด้วยมากที่สุด).3.2 เจ้าหนาที่สรรหาติดตามและแจ้งสถานะการสรรหาอย่างสม่ำเสมอ</t>
   </si>
   <si>
-    <t>เรื่องที่พี่ๆประทับในกระบวนการสรรหา</t>
-  </si>
-  <si>
     <t>เรื่องที่พี่ๆแนะนำให้ปรับปรุงเพื่อพัฒนาคุณภาพการสรรหาให้ดีขึ้น</t>
   </si>
   <si>
@@ -128,9 +126,6 @@
     <t>Credit Analyst</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>น้องฟาง Support ดีมากกมากกก หาน้องมาให้สัมภาษณ์เรื่อยๆ เมื่อน้องสัมภาษณ์ไม่ผ่านก้จะรีบหารายถัดๆไปตลอดเลย</t>
   </si>
   <si>
@@ -143,9 +138,6 @@
     <t>Romrawin Chayalak</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>ทีม HR มีความเข้าใจ requirement ของคุณสมบัติของพนักงานใหม่ที่ทีมต้องการ โดยมีความพยายามอย่างต่อเนื่องและตั้งใจสรรหาจนได้ candidate ตามคุณสมบัติที่ทีมกำหนด</t>
   </si>
   <si>
@@ -222,9 +214,6 @@
   </si>
   <si>
     <t>Risk Management Officer</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>การรับฟังความต้องการลูกค้าและจัดการได้ตามความต้องการ</t>
@@ -257,6 +246,42 @@
   </si>
   <si>
     <t xml:space="preserve">น่าจะมีเงินช่วยเหลือค่าเดินทางให้กับน้องที่มาสัมภาษณ์ เพราะบริษัทเราอยู่ไกลและเดินทางมาลำบากถ้าไม่มีรถส่วนตัวมาเอง </t>
+  </si>
+  <si>
+    <t>เรื่องที่พี่ๆประทับใจในกระบวนการสรรหา</t>
+  </si>
+  <si>
+    <t>sopicha.p@kubota.com</t>
+  </si>
+  <si>
+    <t>Sopicha Poonyathanyaroj</t>
+  </si>
+  <si>
+    <t>marketing communication executive</t>
+  </si>
+  <si>
+    <t>น้องๆ ที่เลือกมา ตรงตามคุณสมบัติอย่างน้อย 70-80% และใช้เวลาน้อยกว่าเดิม</t>
+  </si>
+  <si>
+    <t>ไม่มีค่ะ ทำได้ดีแล้ว</t>
+  </si>
+  <si>
+    <t>phennapa.b@kubota.com</t>
+  </si>
+  <si>
+    <t>Phennapa Bongsinchai</t>
+  </si>
+  <si>
+    <t>Communication Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">มีการส่ง resume lot ใหม่ๆ มาให้หลังจากที่นัดวัน final interview แล้ว แสดงให้เห็นถึงความไม่หยุดที่จะหาโอกาสที่หาคนที่เหมาะสมมากที่สุด </t>
+  </si>
+  <si>
+    <t>Satisfaction Score (%)</t>
+  </si>
+  <si>
+    <t>Overall Satisfaction</t>
   </si>
 </sst>
 </file>
@@ -292,15 +317,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -315,25 +337,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -386,8 +414,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L14" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L14" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:L16" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="11">
       <extLst>
@@ -424,49 +452,49 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ตำแหน่งที่สรรหา" dataDxfId="6">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ตำแหน่งที่สรรหา" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r943fa200cb644d9a93bb4c3dd9510ab3"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ด้านคุณภาพการสรรหา (โดย 1 หมายถึงไม่เห็นด้วย และ 4 เห็นด้วยมากที่สุด).2.1 ผู้สมัครที่ส่งให้พิจารณา มีคุณสมบัติตรงตามความต้องการ" dataDxfId="5">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ด้านคุณภาพการสรรหา (โดย 1 หมายถึงไม่เห็นด้วย และ 4 เห็นด้วยมากที่สุด).2.1 ผู้สมัครที่ส่งให้พิจารณา มีคุณสมบัติตรงตามความต้องการ" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re74f2ebbdf9b4eeb9db4fc47b976b8db"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ด้านคุณภาพการสรรหา (โดย 1 หมายถึงไม่เห็นด้วย และ 4 เห็นด้วยมากที่สุด).2.2 ระยะเวลาในการสรรหาผู้สมัครเหมาะสม" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ด้านคุณภาพการสรรหา (โดย 1 หมายถึงไม่เห็นด้วย และ 4 เห็นด้วยมากที่สุด).2.2 ระยะเวลาในการสรรหาผู้สมัครเหมาะสม" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1be51d13fd48490e9b193451f33b6b3d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="ด้านการบริการ (โดย 1 หมายถึงไม่เห็นด้วย และ 4 เห็นด้วยมากที่สุด).3.1 เจ้าหน้าที่สรรหาตอบสนองและแก้ไขต่อข้อเสนอแนะที่ได้รับเพื่อพัฒนาคุณภาพการสรรหา" dataDxfId="3">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="ด้านการบริการ (โดย 1 หมายถึงไม่เห็นด้วย และ 4 เห็นด้วยมากที่สุด).3.1 เจ้าหน้าที่สรรหาตอบสนองและแก้ไขต่อข้อเสนอแนะที่ได้รับเพื่อพัฒนาคุณภาพการสรรหา" dataDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rd1147432317742d6917b9b194be362a2"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ด้านการบริการ (โดย 1 หมายถึงไม่เห็นด้วย และ 4 เห็นด้วยมากที่สุด).3.2 เจ้าหนาที่สรรหาติดตามและแจ้งสถานะการสรรหาอย่างสม่ำเสมอ" dataDxfId="2">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ด้านการบริการ (โดย 1 หมายถึงไม่เห็นด้วย และ 4 เห็นด้วยมากที่สุด).3.2 เจ้าหนาที่สรรหาติดตามและแจ้งสถานะการสรรหาอย่างสม่ำเสมอ" dataDxfId="0">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r97210733f498417ca3b3519dd0ebc7fb"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="เรื่องที่พี่ๆประทับในกระบวนการสรรหา" dataDxfId="1">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="เรื่องที่พี่ๆประทับใจในกระบวนการสรรหา" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r84bddc4153d14a0fb33e41e887e8bd32"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="เรื่องที่พี่ๆแนะนำให้ปรับปรุงเพื่อพัฒนาคุณภาพการสรรหาให้ดีขึ้น" dataDxfId="0">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="เรื่องที่พี่ๆแนะนำให้ปรับปรุงเพื่อพัฒนาคุณภาพการสรรหาให้ดีขึ้น" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1bc7efa3e53144b2b07b664f53a0b2bd"/>
@@ -477,7 +505,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zp3wzWXIQk-QHTLT2NP2D5hypM5lSwJOkKByoup55W5URTUySUVQWU5HTVpRQ01aNEZJVkpOQ040WS4u" isFormConnected="1" maxResponseId="13" latestEventMarker="11">
+      <xlmsforms:msForm id="zp3wzWXIQk-QHTLT2NP2D5hypM5lSwJOkKByoup55W5URTUySUVQWU5HTVpRQ01aNEZJVkpOQ040WS4u" isFormConnected="1" maxResponseId="15" latestEventMarker="14">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -793,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="10" width="20" style="1" bestFit="1" customWidth="1"/>
@@ -834,10 +862,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -851,31 +879,31 @@
         <v>46111.513668981483</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="7">
+        <v>2</v>
+      </c>
+      <c r="H2" s="7">
+        <v>3</v>
+      </c>
+      <c r="I2" s="7">
+        <v>4</v>
+      </c>
+      <c r="J2" s="7">
+        <v>4</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3">
-        <v>2</v>
-      </c>
-      <c r="H2" s="3">
-        <v>3</v>
-      </c>
-      <c r="I2" s="3">
-        <v>4</v>
-      </c>
-      <c r="J2" s="3">
-        <v>4</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -889,31 +917,31 @@
         <v>46111.560902777775</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="7">
+        <v>4</v>
+      </c>
+      <c r="H3" s="7">
+        <v>4</v>
+      </c>
+      <c r="I3" s="7">
+        <v>4</v>
+      </c>
+      <c r="J3" s="7">
+        <v>4</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="3">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3">
-        <v>4</v>
-      </c>
-      <c r="I3" s="3">
-        <v>4</v>
-      </c>
-      <c r="J3" s="3">
-        <v>4</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -926,32 +954,32 @@
       <c r="C4" s="2">
         <v>46112.745127314804</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="7">
+        <v>4</v>
+      </c>
+      <c r="H4" s="7">
+        <v>3</v>
+      </c>
+      <c r="I4" s="7">
+        <v>4</v>
+      </c>
+      <c r="J4" s="7">
+        <v>3</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="3">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3">
-        <v>3</v>
-      </c>
-      <c r="I4" s="3">
-        <v>4</v>
-      </c>
-      <c r="J4" s="3">
-        <v>3</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -964,32 +992,32 @@
       <c r="C5" s="2">
         <v>46183.408969907403</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="8">
+        <v>4</v>
+      </c>
+      <c r="H5" s="8">
+        <v>4</v>
+      </c>
+      <c r="I5" s="8">
+        <v>4</v>
+      </c>
+      <c r="J5" s="8">
+        <v>4</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="L5" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1002,32 +1030,32 @@
       <c r="C6" s="2">
         <v>46183.423206018502</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="8">
+        <v>4</v>
+      </c>
+      <c r="H6" s="8">
+        <v>3</v>
+      </c>
+      <c r="I6" s="8">
+        <v>4</v>
+      </c>
+      <c r="J6" s="8">
+        <v>4</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1040,32 +1068,32 @@
       <c r="C7" s="2">
         <v>46184.754004629598</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="8">
+        <v>4</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8">
+        <v>3</v>
+      </c>
+      <c r="J7" s="8">
+        <v>4</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1078,32 +1106,32 @@
       <c r="C8" s="2">
         <v>46190.381412037001</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="8">
+        <v>4</v>
+      </c>
+      <c r="H8" s="8">
+        <v>4</v>
+      </c>
+      <c r="I8" s="8">
+        <v>4</v>
+      </c>
+      <c r="J8" s="8">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1116,32 +1144,32 @@
       <c r="C9" s="2">
         <v>46213.546539351897</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="8">
+        <v>4</v>
+      </c>
+      <c r="H9" s="8">
+        <v>3</v>
+      </c>
+      <c r="I9" s="8">
+        <v>4</v>
+      </c>
+      <c r="J9" s="8">
+        <v>4</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1154,32 +1182,32 @@
       <c r="C10" s="2">
         <v>46216.473749999997</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="8">
+        <v>4</v>
+      </c>
+      <c r="H10" s="8">
+        <v>4</v>
+      </c>
+      <c r="I10" s="8">
+        <v>4</v>
+      </c>
+      <c r="J10" s="8">
+        <v>4</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>37</v>
+      <c r="L10" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1192,32 +1220,32 @@
       <c r="C11" s="2">
         <v>46218.824826388904</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>58</v>
+      <c r="F11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="8">
+        <v>4</v>
+      </c>
+      <c r="H11" s="8">
+        <v>4</v>
+      </c>
+      <c r="I11" s="8">
+        <v>4</v>
+      </c>
+      <c r="J11" s="8">
+        <v>3</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="41.4" x14ac:dyDescent="0.25">
@@ -1230,36 +1258,36 @@
       <c r="C12" s="2">
         <v>46225.946111111101</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="8">
+        <v>4</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8">
+        <v>4</v>
+      </c>
+      <c r="J12" s="8">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="L12" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2">
@@ -1268,36 +1296,36 @@
       <c r="C13" s="2">
         <v>46251.3733333333</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="8">
+        <v>3</v>
+      </c>
+      <c r="H13" s="8">
+        <v>4</v>
+      </c>
+      <c r="I13" s="8">
+        <v>4</v>
+      </c>
+      <c r="J13" s="8">
+        <v>4</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2">
@@ -1306,32 +1334,108 @@
       <c r="C14" s="2">
         <v>46251.409861111097</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="D14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="8">
+        <v>4</v>
+      </c>
+      <c r="H14" s="8">
+        <v>4</v>
+      </c>
+      <c r="I14" s="8">
+        <v>4</v>
+      </c>
+      <c r="J14" s="8">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46267.4194907407</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46267.420416666697</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>72</v>
+      </c>
+      <c r="G15" s="8">
+        <v>3</v>
+      </c>
+      <c r="H15" s="8">
+        <v>4</v>
+      </c>
+      <c r="I15" s="8">
+        <v>3</v>
+      </c>
+      <c r="J15" s="8">
+        <v>3</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46267.4686111111</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46267.503518518497</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="8">
+        <v>4</v>
+      </c>
+      <c r="H16" s="8">
+        <v>4</v>
+      </c>
+      <c r="I16" s="8">
+        <v>4</v>
+      </c>
+      <c r="J16" s="8">
+        <v>4</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1343,6 +1447,503 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{910F2308-5976-4C00-8B09-15384BB07B9F}">
+  <dimension ref="A1:D67"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>IF(Sheet1!A2="","",AVERAGE(Sheet1!G2:J2)/4*100)</f>
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>IF(Sheet1!A3="","",AVERAGE(Sheet1!G3:J3)/4*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>IF(Sheet1!A4="","",AVERAGE(Sheet1!G4:J4)/4*100)</f>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f>IF(Sheet1!A5="","",AVERAGE(Sheet1!G5:J5)/4*100)</f>
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f>IF(Sheet1!A6="","",AVERAGE(Sheet1!G6:J6)/4*100)</f>
+        <v>93.75</v>
+      </c>
+      <c r="D6">
+        <f>AVERAGE(B2:B500)</f>
+        <v>92.916666666666671</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f>IF(Sheet1!A7="","",AVERAGE(Sheet1!G7:J7)/4*100)</f>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f>IF(Sheet1!A8="","",AVERAGE(Sheet1!G8:J8)/4*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f>IF(Sheet1!A9="","",AVERAGE(Sheet1!G9:J9)/4*100)</f>
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <f>IF(Sheet1!A10="","",AVERAGE(Sheet1!G10:J10)/4*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <f>IF(Sheet1!A11="","",AVERAGE(Sheet1!G11:J11)/4*100)</f>
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <f>IF(Sheet1!A12="","",AVERAGE(Sheet1!G12:J12)/4*100)</f>
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <f>IF(Sheet1!A13="","",AVERAGE(Sheet1!G13:J13)/4*100)</f>
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <f>IF(Sheet1!A14="","",AVERAGE(Sheet1!G14:J14)/4*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <f>IF(Sheet1!A15="","",AVERAGE(Sheet1!G15:J15)/4*100)</f>
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <f>IF(Sheet1!A16="","",AVERAGE(Sheet1!G16:J16)/4*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <f>IF(Sheet1!A17="","",AVERAGE(Sheet1!G17:J17)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <f>IF(Sheet1!A18="","",AVERAGE(Sheet1!G18:J18)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <f>IF(Sheet1!A19="","",AVERAGE(Sheet1!G19:J19)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <f>IF(Sheet1!A20="","",AVERAGE(Sheet1!G20:J20)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <f>IF(Sheet1!A21="","",AVERAGE(Sheet1!G21:J21)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <f>IF(Sheet1!A22="","",AVERAGE(Sheet1!G22:J22)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <f>IF(Sheet1!A23="","",AVERAGE(Sheet1!G23:J23)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <f>IF(Sheet1!A24="","",AVERAGE(Sheet1!G24:J24)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <f>IF(Sheet1!A25="","",AVERAGE(Sheet1!G25:J25)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="str">
+        <f>IF(Sheet1!A26="","",AVERAGE(Sheet1!G26:J26)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="str">
+        <f>IF(Sheet1!A27="","",AVERAGE(Sheet1!G27:J27)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="str">
+        <f>IF(Sheet1!A28="","",AVERAGE(Sheet1!G28:J28)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" t="str">
+        <f>IF(Sheet1!A29="","",AVERAGE(Sheet1!G29:J29)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="str">
+        <f>IF(Sheet1!A30="","",AVERAGE(Sheet1!G30:J30)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="str">
+        <f>IF(Sheet1!A31="","",AVERAGE(Sheet1!G31:J31)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" t="str">
+        <f>IF(Sheet1!A32="","",AVERAGE(Sheet1!G32:J32)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="str">
+        <f>IF(Sheet1!A33="","",AVERAGE(Sheet1!G33:J33)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="str">
+        <f>IF(Sheet1!A34="","",AVERAGE(Sheet1!G34:J34)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="str">
+        <f>IF(Sheet1!A35="","",AVERAGE(Sheet1!G35:J35)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="str">
+        <f>IF(Sheet1!A36="","",AVERAGE(Sheet1!G36:J36)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" t="str">
+        <f>IF(Sheet1!A37="","",AVERAGE(Sheet1!G37:J37)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" t="str">
+        <f>IF(Sheet1!A38="","",AVERAGE(Sheet1!G38:J38)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" t="str">
+        <f>IF(Sheet1!A39="","",AVERAGE(Sheet1!G39:J39)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" t="str">
+        <f>IF(Sheet1!A40="","",AVERAGE(Sheet1!G40:J40)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" t="str">
+        <f>IF(Sheet1!A41="","",AVERAGE(Sheet1!G41:J41)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" t="str">
+        <f>IF(Sheet1!A42="","",AVERAGE(Sheet1!G42:J42)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" t="str">
+        <f>IF(Sheet1!A43="","",AVERAGE(Sheet1!G43:J43)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" t="str">
+        <f>IF(Sheet1!A44="","",AVERAGE(Sheet1!G44:J44)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" t="str">
+        <f>IF(Sheet1!A45="","",AVERAGE(Sheet1!G45:J45)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" t="str">
+        <f>IF(Sheet1!A46="","",AVERAGE(Sheet1!G46:J46)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" t="str">
+        <f>IF(Sheet1!A47="","",AVERAGE(Sheet1!G47:J47)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" t="str">
+        <f>IF(Sheet1!A48="","",AVERAGE(Sheet1!G48:J48)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" t="str">
+        <f>IF(Sheet1!A49="","",AVERAGE(Sheet1!G49:J49)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" t="str">
+        <f>IF(Sheet1!A50="","",AVERAGE(Sheet1!G50:J50)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" t="str">
+        <f>IF(Sheet1!A51="","",AVERAGE(Sheet1!G51:J51)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" t="str">
+        <f>IF(Sheet1!A52="","",AVERAGE(Sheet1!G52:J52)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" t="str">
+        <f>IF(Sheet1!A53="","",AVERAGE(Sheet1!G53:J53)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" t="str">
+        <f>IF(Sheet1!A54="","",AVERAGE(Sheet1!G54:J54)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" t="str">
+        <f>IF(Sheet1!A55="","",AVERAGE(Sheet1!G55:J55)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" t="str">
+        <f>IF(Sheet1!A56="","",AVERAGE(Sheet1!G56:J56)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" t="str">
+        <f>IF(Sheet1!A57="","",AVERAGE(Sheet1!G57:J57)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" t="str">
+        <f>IF(Sheet1!A58="","",AVERAGE(Sheet1!G58:J58)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" t="str">
+        <f>IF(Sheet1!A59="","",AVERAGE(Sheet1!G59:J59)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" t="str">
+        <f>IF(Sheet1!A60="","",AVERAGE(Sheet1!G60:J60)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" t="str">
+        <f>IF(Sheet1!A61="","",AVERAGE(Sheet1!G61:J61)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" t="str">
+        <f>IF(Sheet1!A62="","",AVERAGE(Sheet1!G62:J62)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" t="str">
+        <f>IF(Sheet1!A63="","",AVERAGE(Sheet1!G63:J63)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" t="str">
+        <f>IF(Sheet1!A64="","",AVERAGE(Sheet1!G64:J64)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" t="str">
+        <f>IF(Sheet1!A65="","",AVERAGE(Sheet1!G65:J65)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" t="str">
+        <f>IF(Sheet1!A66="","",AVERAGE(Sheet1!G66:J66)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" t="str">
+        <f>IF(Sheet1!A67="","",AVERAGE(Sheet1!G67:J67)/4*100)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{cdf09dce-c865-4f42-901d-32d3d8d3f60f}" enabled="0" method="" siteId="{cdf09dce-c865-4f42-901d-32d3d8d3f60f}" removed="1"/>
